--- a/out/LSTM-Mamba1_repeat_2_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9470245394981236</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.729251253104852</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.729251253104852</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.729251253104852</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.729251253104852</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.729251253104852</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.729251253104852</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.729251253104852</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.729251253104852</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.729251253104852</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.729251253104852</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.729251253104852</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.729251253104852</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.729251253104852</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>-5.113152705365792e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.06581025827228758</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>-5.403607925167307e-06</v>
+        <v>0.1317450612097988</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.001403691536595765</v>
+        <v>-0.01519829364927153</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.001409095144520863</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.001409095144520863</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.001429258147846907</v>
+        <v>0.05049346794002224</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0619449445875259</v>
+        <v>0.2069603280649097</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.1225843030746463</v>
+        <v>0.4648262304554276</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01185252926938394</v>
+        <v>0.03959946472118359</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.08425369549022685</v>
+        <v>0.3367629381030302</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.02076082908655722</v>
+        <v>0.0693624355333953</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.113928634412657</v>
+        <v>0.4359076316691118</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0113685586967788</v>
+        <v>0.0379851555764479</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.1158878549493477</v>
+        <v>0.4424561980214322</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.004692314361594591</v>
+        <v>0.01568861925315071</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.1138947841203855</v>
+        <v>0.4358079836439788</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.00584765877138694</v>
+        <v>0.0195461828627473</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.1208980240800092</v>
+        <v>0.4592153450370701</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.003518446461214584</v>
+        <v>0.01176817925537965</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.1220852643454336</v>
+        <v>0.463193604961955</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.002673741879488273</v>
+        <v>0.008945698889074837</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.1239137133228115</v>
+        <v>0.4693134159177437</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.001180611880909337</v>
+        <v>0.003953926535315225</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.1235975078509301</v>
+        <v>0.4682690490630101</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0009357850063436491</v>
+        <v>0.003137675919314173</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.1242881244977647</v>
+        <v>0.470587744349756</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.0004602753289747387</v>
+        <v>0.001553422204039044</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.1242747997314455</v>
+        <v>0.4705549303812415</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0002655556693435473</v>
+        <v>0.0008997614318907874</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.124345798203967</v>
+        <v>0.470803118930717</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0001317324350445884</v>
+        <v>0.0004488353163182084</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1243406279628552</v>
+        <v>0.470797553875112</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>6.111690773477915e-05</v>
+        <v>0.0002192225566657728</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1243339196856525</v>
+        <v>0.4707868779063155</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>3.505183333483284e-05</v>
+        <v>0.0001251684583382067</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.124339995504041</v>
+        <v>0.4708178743160781</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>8.391820683831448e-06</v>
+        <v>3.740743216546624e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.1243216945201252</v>
+        <v>0.4707696475226011</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.73737344181313e-06</v>
+        <v>1.745791147271043e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.124316769070646</v>
+        <v>0.470764896024337</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>-2.553803869891494e-06</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.124312367942041</v>
+        <v>0.4707618871525233</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.629819553036738e-06</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.1243072127534682</v>
+        <v>0.4707565006683657</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.1243077524213684</v>
+        <v>0.4707531160499149</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.1243074203180452</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1243078008531029</v>
+        <v>0.4707478291546989</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1243080291741376</v>
+        <v>0.4707480574757336</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.1243081191187876</v>
+        <v>0.4707481474203835</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.1243072611852027</v>
+        <v>0.4707472894867987</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.1243074895062374</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.1243066938420257</v>
+        <v>0.4707467221436217</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1243067561113988</v>
+        <v>0.4707467844129947</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.1243067837866757</v>
+        <v>0.4707468120882716</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.1243069360006989</v>
+        <v>0.4707469643022949</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.1243065900597372</v>
+        <v>0.4707466183613331</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.1243066661667488</v>
+        <v>0.4707466944683448</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.1243068322184104</v>
+        <v>0.4707468605200064</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1243071919970105</v>
+        <v>0.4707472202986064</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1243072127534682</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1243073165357567</v>
+        <v>0.4707473448373526</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.1243075448567914</v>
+        <v>0.4707475731583873</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1243074203180452</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.124307447993322</v>
+        <v>0.470747476294918</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.124307503343876</v>
+        <v>0.470747531645472</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.1243077662590067</v>
+        <v>0.4707477945606026</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1243076832331759</v>
+        <v>0.4707477115347719</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1243074756685991</v>
+        <v>0.470747503970195</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.1243074895062374</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.1243076278826222</v>
+        <v>0.4707476561842181</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1243073442110336</v>
+        <v>0.4707473725126295</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1243071712405528</v>
+        <v>0.4707471995421487</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1243070674582643</v>
+        <v>0.4707470957598602</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.1243072127534682</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.1243074549121414</v>
+        <v>0.4707474832137374</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.1243072819416604</v>
+        <v>0.4707473102432564</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.1243069844324335</v>
+        <v>0.4707470127340295</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.124306970594795</v>
+        <v>0.4707469988963909</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.1243066038973758</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.1243066038973758</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1243065416280027</v>
+        <v>0.4707465699295986</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1243064378457142</v>
+        <v>0.4707464661473101</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.1243062648752334</v>
+        <v>0.4707462931768294</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.124306313306968</v>
+        <v>0.4707463416085639</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1243059535283679</v>
+        <v>0.4707459818299639</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1243059120154525</v>
+        <v>0.4707459403170485</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1243059673660062</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.1243060227165602</v>
+        <v>0.4707460510181561</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.1243060642294756</v>
+        <v>0.4707460925310715</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1243057943955255</v>
+        <v>0.4707458226971214</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.1243058497460794</v>
+        <v>0.4707458780476754</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1243059950412833</v>
+        <v>0.4707460233428792</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1243059604471871</v>
+        <v>0.470745988748783</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1243059466095485</v>
+        <v>0.4707459749111444</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1243060365541987</v>
+        <v>0.4707460648557947</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1243063548198834</v>
+        <v>0.4707463831214793</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1243061749305832</v>
+        <v>0.4707462032321791</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1243062164434986</v>
+        <v>0.4707462447450946</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1243060296353793</v>
+        <v>0.4707460579369753</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1243060988235718</v>
+        <v>0.4707461271251678</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.124305898177814</v>
+        <v>0.4707459264794099</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1243059396907294</v>
+        <v>0.4707459679923253</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1243059673660062</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_2_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.3566176397962524</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534076</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.729251253104852</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.729251253104852</v>
+        <v>2.037200859271898</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.729251253104852</v>
+        <v>2.037200859271898</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.729251253104852</v>
+        <v>2.037200859271898</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.729251253104852</v>
+        <v>2.037200859271898</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.729251253104852</v>
+        <v>2.037200859271898</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.729251253104852</v>
+        <v>2.037200859271898</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.729251253104852</v>
+        <v>2.037200859271898</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.729251253104852</v>
+        <v>2.037200859271898</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.729251253104852</v>
+        <v>2.037200859271898</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.729251253104852</v>
+        <v>2.037200859271898</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.729251253104852</v>
+        <v>2.037200859271898</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.729251253104852</v>
+        <v>1.196909249534075</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.3566176397962525</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>-4.447939541039523e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.05724823620907817</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC45" t="n">
-        <v>-5.403607925167307e-06</v>
+        <v>0.1146052355035185</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.001403691536595765</v>
+        <v>-0.01322106803684416</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.001409095144520863</v>
+        <v>0.04398268877682358</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.001409095144520863</v>
+        <v>0.04398268877682358</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.001429258147846907</v>
+        <v>0.04392084386913839</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0619449445875259</v>
+        <v>0.1900009315651253</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.1225843030746463</v>
+        <v>0.4243010432626593</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01185252926938394</v>
+        <v>0.0363545373902973</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.08425369549022685</v>
+        <v>0.3067319173023389</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.02076082908655722</v>
+        <v>0.06367820249731102</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.113928634412657</v>
+        <v>0.3977520411007891</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0113685586967788</v>
+        <v>0.03487250097524913</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.1158878549493477</v>
+        <v>0.4037639953038872</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.004692314361594591</v>
+        <v>0.01440304757237217</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.1138947841203855</v>
+        <v>0.3976605551983751</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.00584765877138694</v>
+        <v>0.01794447086882587</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.1208980240800092</v>
+        <v>0.4191498485069515</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.003518446461214584</v>
+        <v>0.01080401684345775</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.1220852643454336</v>
+        <v>0.4228017158579607</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.002673741879488273</v>
+        <v>0.008212683002534785</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.1239137133228115</v>
+        <v>0.428419371168545</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.001180611880909337</v>
+        <v>0.003629710953940554</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.1235975078509301</v>
+        <v>0.4274603136428171</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0009357850063436491</v>
+        <v>0.002877888102549037</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.1242881244977647</v>
+        <v>0.4295878557995856</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.0004602753289747387</v>
+        <v>0.001425846710610487</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.1242747997314455</v>
+        <v>0.4295573187370007</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0002655556693435473</v>
+        <v>0.0008270314132500488</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.124345798203967</v>
+        <v>0.4297847791131881</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0001317324350445884</v>
+        <v>0.0004110157066250244</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1243406279628552</v>
+        <v>0.4297792611455503</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>6.111690773477915e-05</v>
+        <v>0.0001991000195291009</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1243339196856525</v>
+        <v>0.4297690599644725</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>3.505183333483284e-05</v>
+        <v>0.0001151555000044985</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.124339995504041</v>
+        <v>0.4297972874196379</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>8.391820683831448e-06</v>
+        <v>3.517546205149434e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.1243216945201252</v>
+        <v>0.4297523844678907</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.73737344181313e-06</v>
+        <v>1.521212032543939e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.124316769070646</v>
+        <v>0.4297476081194531</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>-2.553803869891494e-06</v>
+        <v>4.784784520434025e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.124312367942041</v>
+        <v>0.4297444016677597</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.629819553036738e-06</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.1243072127534682</v>
+        <v>0.4297390151836022</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.1243077524213684</v>
+        <v>0.4297356305651513</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.1243074203180452</v>
+        <v>0.4297299631348776</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1243078008531029</v>
+        <v>0.4297303436699353</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1243080291741376</v>
+        <v>0.42973057199097</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.1243081191187876</v>
+        <v>0.42973066193562</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.1243072611852027</v>
+        <v>0.4297298040020352</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.1243074895062374</v>
+        <v>0.4297300323230699</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.1243066938420257</v>
+        <v>0.4297292366588581</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1243067561113988</v>
+        <v>0.4297292989282313</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.1243067837866757</v>
+        <v>0.4297293266035081</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.1243069360006989</v>
+        <v>0.4297294788175314</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.1243065900597372</v>
+        <v>0.4297291328765697</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.1243066661667488</v>
+        <v>0.4297292089835813</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.1243068322184104</v>
+        <v>0.4297293750352429</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1243071919970105</v>
+        <v>0.4297297348138429</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1243072127534682</v>
+        <v>0.4297297555703006</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1243073165357567</v>
+        <v>0.4297298593525891</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.1243075448567914</v>
+        <v>0.4297300876736238</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1243074203180452</v>
+        <v>0.4297299631348776</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.124307447993322</v>
+        <v>0.4297299908101544</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.124307503343876</v>
+        <v>0.4297300461607084</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.1243077662590067</v>
+        <v>0.4297303090758391</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1243076832331759</v>
+        <v>0.4297302260500083</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1243074756685991</v>
+        <v>0.4297300184854316</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.1243074895062374</v>
+        <v>0.4297300323230699</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.1243076278826222</v>
+        <v>0.4297301706994546</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1243073442110336</v>
+        <v>0.429729887027866</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1243071712405528</v>
+        <v>0.4297297140573852</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1243070674582643</v>
+        <v>0.4297296102750967</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.1243072127534682</v>
+        <v>0.4297297555703006</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.1243074549121414</v>
+        <v>0.4297299977289739</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.1243072819416604</v>
+        <v>0.4297298247584929</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.1243069844324335</v>
+        <v>0.4297295272492659</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.124306970594795</v>
+        <v>0.4297295134116274</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.1243066038973758</v>
+        <v>0.4297291467142082</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.1243066038973758</v>
+        <v>0.4297291467142082</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1243065416280027</v>
+        <v>0.4297290844448351</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1243064378457142</v>
+        <v>0.4297289806625466</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.1243062648752334</v>
+        <v>0.4297288076920658</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.124306313306968</v>
+        <v>0.4297288561238004</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1243059535283679</v>
+        <v>0.4297284963452003</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1243059120154525</v>
+        <v>0.4297284548322849</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1243059673660062</v>
+        <v>0.4297285101828386</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.1243060227165602</v>
+        <v>0.4297285655333926</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.1243060642294756</v>
+        <v>0.429728607046308</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1243057943955255</v>
+        <v>0.4297283372123579</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.1243058497460794</v>
+        <v>0.4297283925629118</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1243059950412833</v>
+        <v>0.4297285378581158</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1243059604471871</v>
+        <v>0.4297285032640195</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1243059466095485</v>
+        <v>0.429728489426381</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1243060365541987</v>
+        <v>0.4297285793710311</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1243063548198834</v>
+        <v>0.4297288976367158</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1243061749305832</v>
+        <v>0.4297287177474157</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1243062164434986</v>
+        <v>0.4297287592603311</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1243060296353793</v>
+        <v>0.4297285724522117</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1243060988235718</v>
+        <v>0.4297286416404043</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.124305898177814</v>
+        <v>0.4297284409946464</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1243059396907294</v>
+        <v>0.4297284825075618</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1243059673660062</v>
+        <v>0.4297285101828386</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_2_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.01051885448396206</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-1.14</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.005836124531924725</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999996</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.003148936666548252</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.001595830544829369</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.0007980000227689743</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.0003222525119781494</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0001088622957468033</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.3566176397962524</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>6.740912795066833e-05</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.396909249534076</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.0001782495528459549</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.237200859271899</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0001839771866798401</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.237200859271899</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.0001905746757984161</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.237200859271899</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.0001968443393707275</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.237200859271899</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0002832487225532532</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.237200859271899</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0002821125090122223</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.237200859271899</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0002665892243385315</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.237200859271899</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.0002687517553567886</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.237200859271899</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.0003303848206996918</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.237200859271899</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.0003962535411119461</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.037200859271898</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.0004607997834682465</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.037200859271898</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.0004006847739219666</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.037200859271898</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.0003127604722976685</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.037200859271898</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0002534948289394379</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.037200859271898</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.0002538338303565979</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.037200859271898</v>
+        <v>-0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.0003492124378681183</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.037200859271898</v>
+        <v>-0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0003297515213489532</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.037200859271898</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.0004204455763101578</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.037200859271898</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.0005108248442411423</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.037200859271898</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0003423839807510376</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.037200859271898</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>9.636767208576202e-05</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.196909249534075</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-4.39472496509552e-05</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.3566176397962525</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.0001721717417240143</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.0002499260008335114</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.000231470912694931</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-8.131936192512512e-05</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-9.419023990631104e-05</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.0001608598977327347</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.0001751650124788284</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.0002722572535276413</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.0003269575536251068</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0003323331475257874</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.0002726707607507706</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.0002636630088090897</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.0003355219960212708</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-4.447939541039523e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.05724823620907817</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.0007386412471532822</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1146052355035185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.01322106803684416</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.001329954713582993</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.04398268877682358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.001553338021039963</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.04398268877682358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.001633383333683014</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.04392084386913839</v>
+        <v>-1.572706125420518e-05</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.1900009315651253</v>
+        <v>0.0483169334537267</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.001820601522922516</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.4243010432626593</v>
+        <v>0.09671435015372233</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0363545373902973</v>
+        <v>0.00924483870115754</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.001792345196008682</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.3067319173023389</v>
+        <v>0.06681670935983816</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.06367820249731102</v>
+        <v>0.01619342928458149</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.001900933682918549</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.3977520411007891</v>
+        <v>0.08996313684407575</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.03487250097524913</v>
+        <v>0.008866366249509762</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.002084538340568542</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.4037639953038872</v>
+        <v>0.09149022721617087</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01440304757237217</v>
+        <v>0.003659054835664152</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.002256616950035095</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.3976605551983751</v>
+        <v>0.08993453340209276</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.01794447086882587</v>
+        <v>0.004559387025061533</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.002285370603203773</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4191498485069515</v>
+        <v>0.09539572624475672</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01080401684345775</v>
+        <v>0.002743335502610705</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.002659710124135017</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.4228017158579607</v>
+        <v>0.09632073378365487</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.008212683002534785</v>
+        <v>0.002084454598152154</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.002988105639815331</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.428419371168545</v>
+        <v>0.09774598404177814</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.003629710953940554</v>
+        <v>0.0009199679821571501</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.003663003444671631</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4274603136428171</v>
+        <v>0.09749819371384895</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.002877888102549037</v>
+        <v>0.0007289636376568415</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.004290072247385979</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.4295878557995856</v>
+        <v>0.09803588659381936</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001425846710610487</v>
+        <v>0.0003577146381792318</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.004265249706804752</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.4295573187370007</v>
+        <v>0.09802439228128665</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0008270314132500488</v>
+        <v>0.0002073716544309565</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.004545849747955799</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4297847791131881</v>
+        <v>0.09807872657311079</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0004110157066250244</v>
+        <v>9.973122684266348e-05</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.00543409027159214</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4297792611455503</v>
+        <v>0.0980735961756634</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0001991000195291009</v>
+        <v>4.674366692287064e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.006070714443922043</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4297690599644725</v>
+        <v>0.0980672517426142</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001151555000044985</v>
+        <v>2.503887500112463e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.006617431528866291</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4297972874196379</v>
+        <v>0.09807102216729405</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>3.517546205149434e-05</v>
+        <v>6.159850569859539e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.006957695819437504</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4297523844678907</v>
+        <v>0.09805493801403116</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.521212032543939e-05</v>
+        <v>-5.08417705457914e-07</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.006962105631828308</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4297476081194531</v>
+        <v>0.09805000155201671</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.784784520434025e-06</v>
+        <v>-2.553803869891494e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.006884505972266197</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4297444016677597</v>
+        <v>0.09804560042341171</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.596391060734771e-07</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.006567009724676609</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4297390151836022</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.006447156891226768</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4297356305651513</v>
+        <v>0.09804098490273906</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.006371449679136276</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4297299631348776</v>
+        <v>0.09804065279941587</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.006333786062896252</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4297303436699353</v>
+        <v>0.09804103333447362</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.00658302940428257</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.42973057199097</v>
+        <v>0.0980412616555083</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.006845145486295223</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.42973066193562</v>
+        <v>0.09804135160015826</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.006835383363068104</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4297298040020352</v>
+        <v>0.09804049366657343</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.006729091517627239</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4297300323230699</v>
+        <v>0.09804072198760812</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.006421317346394062</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4297292366588581</v>
+        <v>0.09803992632339639</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.006194060668349266</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4297292989282313</v>
+        <v>0.09803998859276948</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.005918755196034908</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4297293266035081</v>
+        <v>0.09804001626804634</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.005646701902151108</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4297294788175314</v>
+        <v>0.09804016848206963</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.00551874190568924</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4297291328765697</v>
+        <v>0.09803982254110789</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.00534225907176733</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.16</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4297292089835813</v>
+        <v>0.09803989864811953</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.005270667374134064</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4297293750352429</v>
+        <v>0.09804006469978113</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.005089147947728634</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4297297348138429</v>
+        <v>0.09804042447838117</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.005072087980806828</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4297297555703006</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.005149140954017639</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4297298593525891</v>
+        <v>0.09804054901712737</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.005506232380867004</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4297300876736238</v>
+        <v>0.09804077733816206</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.005831675603985786</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4297299631348776</v>
+        <v>0.09804065279941587</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.006008099764585495</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4297299908101544</v>
+        <v>0.09804068047469272</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.005933886393904686</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4297300461607084</v>
+        <v>0.09804073582524667</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.006064223125576973</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4297303090758391</v>
+        <v>0.09804099874037737</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.00615039374679327</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4297302260500083</v>
+        <v>0.09804091571454657</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.006163754500448704</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4297300184854316</v>
+        <v>0.0980407081499698</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.006134302355349064</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4297300323230699</v>
+        <v>0.09804072198760812</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.006138771772384644</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4297301706994546</v>
+        <v>0.09804086036399286</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.0061269486322999</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.16</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.429729887027866</v>
+        <v>0.09804057669240422</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.006039709784090519</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4297297140573852</v>
+        <v>0.09804040372192348</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.005777085199952126</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4297296102750967</v>
+        <v>0.09804029993963498</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.005616120994091034</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4297297555703006</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.005607175640761852</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4297299977289739</v>
+        <v>0.09804068739351211</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.005672729574143887</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4297298247584929</v>
+        <v>0.09804051442303113</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.005629505030810833</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4297295272492659</v>
+        <v>0.09804021691380418</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.005536997690796852</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4297295134116274</v>
+        <v>0.09804020307616564</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.005343656055629253</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4297291467142082</v>
+        <v>0.09803983637874643</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.005072209052741528</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4297291467142082</v>
+        <v>0.09803983637874643</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.004878522828221321</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4297290844448351</v>
+        <v>0.09803977410937334</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.004797053523361683</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4297289806625466</v>
+        <v>0.09803967032708484</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.004662945866584778</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4297288076920658</v>
+        <v>0.09803949735660408</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.004520243965089321</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4297288561238004</v>
+        <v>0.09803954578833864</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.004333194345235825</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4297284963452003</v>
+        <v>0.0980391860097386</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.004098003730177879</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4297284548322849</v>
+        <v>0.09803914449682319</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.003852915018796921</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4297285101828386</v>
+        <v>0.09803919984737691</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.003748527728021145</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4297285655333926</v>
+        <v>0.09803925519793084</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003690445795655251</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.429728607046308</v>
+        <v>0.09803929671084624</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.003592804074287415</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4297283372123579</v>
+        <v>0.09803902687689615</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.00345512293279171</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4297283925629118</v>
+        <v>0.0980390822274501</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003404975868761539</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4297285378581158</v>
+        <v>0.098039227522654</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.00336892157793045</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4297285032640195</v>
+        <v>0.09803919292855776</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.003369292244315147</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.429728489426381</v>
+        <v>0.09803917909091921</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.003233139403164387</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4297285793710311</v>
+        <v>0.09803926903556939</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003182061016559601</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4297288976367158</v>
+        <v>0.09803958730125403</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003499255515635014</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4297287177474157</v>
+        <v>0.0980394074119539</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003777755424380302</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4297287592603311</v>
+        <v>0.09803944892486929</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003874681890010834</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4297285724522117</v>
+        <v>0.09803926211675</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.003947744145989418</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4297286416404043</v>
+        <v>0.0980393313049425</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.00387246161699295</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4297284409946464</v>
+        <v>0.09803913065918465</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.00377553328871727</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.01999999999999985</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4297284825075618</v>
+        <v>0.09803917217210005</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.003649835474789143</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4297285101828386</v>
+        <v>0.09803919984737691</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_2_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.01051885448396206</v>
+        <v>-0.01051884517073631</v>
       </c>
       <c r="JB2" t="n">
         <v>-1.14</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.005836124531924725</v>
+        <v>-0.005836115218698978</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.7199999999999996</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.003148936666548252</v>
+        <v>-0.003148922696709633</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.3</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.001595830544829369</v>
+        <v>-0.001595817506313324</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.02000000000000007</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.0007980000227689743</v>
+        <v>-0.0007979869842529297</v>
       </c>
       <c r="JB6" t="n">
         <v>0.8599999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.0003222525119781494</v>
+        <v>-0.000322248786687851</v>
       </c>
       <c r="JB7" t="n">
         <v>0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.0001088622957468033</v>
+        <v>-0.0001088473945856094</v>
       </c>
       <c r="JB8" t="n">
         <v>0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>6.740912795066833e-05</v>
+        <v>6.742216646671295e-05</v>
       </c>
       <c r="JB9" t="n">
         <v>0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.0001782495528459549</v>
+        <v>0.0001782644540071487</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.0001839771866798401</v>
+        <v>0.0001839958131313324</v>
       </c>
       <c r="JB11" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.0001905746757984161</v>
+        <v>0.0001906026154756546</v>
       </c>
       <c r="JB12" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.0001968443393707275</v>
+        <v>0.0001968797296285629</v>
       </c>
       <c r="JB13" t="n">
         <v>0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.0002832487225532532</v>
+        <v>0.0002832747995853424</v>
       </c>
       <c r="JB14" t="n">
         <v>0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.0002821125090122223</v>
+        <v>0.0002821329981088638</v>
       </c>
       <c r="JB15" t="n">
         <v>0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.0002665892243385315</v>
+        <v>0.0002666022628545761</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3999999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.0002687517553567886</v>
+        <v>0.0002687573432922363</v>
       </c>
       <c r="JB17" t="n">
         <v>0.3999999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.0003303848206996918</v>
+        <v>0.0003303941339254379</v>
       </c>
       <c r="JB18" t="n">
         <v>0.3999999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.0003962535411119461</v>
+        <v>0.0003962665796279907</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3999999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.0004607997834682465</v>
+        <v>0.0004608072340488434</v>
       </c>
       <c r="JB20" t="n">
         <v>0.3999999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.0004006847739219666</v>
+        <v>0.0004006940871477127</v>
       </c>
       <c r="JB21" t="n">
         <v>0.2599999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.0003127604722976685</v>
+        <v>0.0003127772361040115</v>
       </c>
       <c r="JB22" t="n">
         <v>0.1199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.0002534948289394379</v>
+        <v>0.0002535227686166763</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.02000000000000007</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.0002538338303565979</v>
+        <v>0.0002538543194532394</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.16</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.0003492124378681183</v>
+        <v>0.0003492143005132675</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.16</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.0003297515213489532</v>
+        <v>0.0003297589719295502</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.02000000000000007</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.0004204455763101578</v>
+        <v>0.0004204660654067993</v>
       </c>
       <c r="JB27" t="n">
         <v>0.1199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.0005108248442411423</v>
+        <v>0.0005108322948217392</v>
       </c>
       <c r="JB28" t="n">
         <v>0.1199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.0003423839807510376</v>
+        <v>0.0003424081951379776</v>
       </c>
       <c r="JB29" t="n">
         <v>0.7199999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>9.636767208576202e-05</v>
+        <v>9.63844358921051e-05</v>
       </c>
       <c r="JB30" t="n">
         <v>0.5799999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-4.39472496509552e-05</v>
+        <v>-4.392676055431366e-05</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.0001721717417240143</v>
+        <v>-0.0001721624284982681</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.5799999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.0002499260008335114</v>
+        <v>-0.0002499129623174667</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.7199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.000231470912694931</v>
+        <v>-0.000231454148888588</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.8599999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-8.131936192512512e-05</v>
+        <v>-8.130818605422974e-05</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.9999999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-9.419023990631104e-05</v>
+        <v>-9.418278932571411e-05</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.9999999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.0001608598977327347</v>
+        <v>-0.0001608561724424362</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.9999999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.0001751650124788284</v>
+        <v>-0.000175153836607933</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.0002722572535276413</v>
+        <v>-0.0002722460776567459</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.0003269575536251068</v>
+        <v>-0.0003269463777542114</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.0003323331475257874</v>
+        <v>-0.0003323238343000412</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.0002636630088090897</v>
+        <v>-0.0002636611461639404</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.0003355219960212708</v>
+        <v>-0.0003355182707309723</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.0007386412471532822</v>
+        <v>-0.0007386263459920883</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.001329954713582993</v>
+        <v>-0.001329949125647545</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.001553338021039963</v>
+        <v>-0.001553339883685112</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.001633383333683014</v>
+        <v>-0.001633372157812119</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.001820601522922516</v>
+        <v>-0.001820599660277367</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.001792345196008682</v>
+        <v>-0.001792343333363533</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.001900933682918549</v>
+        <v>-0.001900937408208847</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.002084538340568542</v>
+        <v>-0.002084512263536453</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.002256616950035095</v>
+        <v>-0.002256607636809349</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.002285370603203773</v>
+        <v>-0.002285381779074669</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.002659710124135017</v>
+        <v>-0.002659713849425316</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.002988105639815331</v>
+        <v>-0.002988139167428017</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.004290072247385979</v>
+        <v>-0.004290096461772919</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.004265249706804752</v>
+        <v>-0.004265273921191692</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.004545849747955799</v>
+        <v>-0.004545936360955238</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.00543409027159214</v>
+        <v>-0.005434125661849976</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.006070714443922043</v>
+        <v>-0.006070785224437714</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.006617431528866291</v>
+        <v>-0.006617510691285133</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.006957695819437504</v>
+        <v>-0.006957723759114742</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.006962105631828308</v>
+        <v>-0.006962141953408718</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.006884505972266197</v>
+        <v>-0.00688453484326601</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.006567009724676609</v>
+        <v>-0.006567026488482952</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.006447156891226768</v>
+        <v>-0.006447167135775089</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.006371449679136276</v>
+        <v>-0.006371360272169113</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.006333786062896252</v>
+        <v>-0.006333745084702969</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.00658302940428257</v>
+        <v>-0.006583034060895443</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.006845145486295223</v>
+        <v>-0.006845148280262947</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.006835383363068104</v>
+        <v>-0.00683538056910038</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.006729091517627239</v>
+        <v>-0.006729076616466045</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.006421317346394062</v>
+        <v>-0.006421319209039211</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.006194060668349266</v>
+        <v>-0.006194059737026691</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.005918755196034908</v>
+        <v>-0.005918765440583229</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.005646701902151108</v>
+        <v>-0.005646656267344952</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.2599999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.00551874190568924</v>
+        <v>-0.005518756806850433</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.1199999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.00534225907176733</v>
+        <v>-0.005342286080121994</v>
       </c>
       <c r="JB80" t="n">
         <v>0.16</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.005270667374134064</v>
+        <v>-0.005270715802907944</v>
       </c>
       <c r="JB81" t="n">
         <v>0.4399999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.005089147947728634</v>
+        <v>-0.005089204758405685</v>
       </c>
       <c r="JB82" t="n">
         <v>0.7199999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.005072087980806828</v>
+        <v>-0.005072047002613544</v>
       </c>
       <c r="JB83" t="n">
         <v>0.7199999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.005149140954017639</v>
+        <v>-0.005149118602275848</v>
       </c>
       <c r="JB84" t="n">
         <v>0.7199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.005506232380867004</v>
+        <v>-0.005506241694092751</v>
       </c>
       <c r="JB85" t="n">
         <v>0.5799999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.005831675603985786</v>
+        <v>-0.005831707268953323</v>
       </c>
       <c r="JB86" t="n">
         <v>0.4399999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.006008099764585495</v>
+        <v>-0.006008142605423927</v>
       </c>
       <c r="JB87" t="n">
         <v>0.3</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.005933886393904686</v>
+        <v>-0.005933924578130245</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.006064223125576973</v>
+        <v>-0.00606426689773798</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.00615039374679327</v>
+        <v>-0.006150435656309128</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.3</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.006163754500448704</v>
+        <v>-0.006163801066577435</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.3</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.006134302355349064</v>
+        <v>-0.006134320981800556</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.3</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.006138771772384644</v>
+        <v>-0.006138746626675129</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.3</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.0061269486322999</v>
+        <v>-0.006126927211880684</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.16</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.006039709784090519</v>
+        <v>-0.006039733998477459</v>
       </c>
       <c r="JB95" t="n">
         <v>0.5799999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.005777085199952126</v>
+        <v>-0.005777092650532722</v>
       </c>
       <c r="JB96" t="n">
         <v>0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.005616120994091034</v>
+        <v>-0.005616177804768085</v>
       </c>
       <c r="JB97" t="n">
         <v>0.8599999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.005607175640761852</v>
+        <v>-0.005607242695987225</v>
       </c>
       <c r="JB98" t="n">
         <v>0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.005672729574143887</v>
+        <v>-0.00567278265953064</v>
       </c>
       <c r="JB99" t="n">
         <v>0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.005629505030810833</v>
+        <v>-0.005629526451230049</v>
       </c>
       <c r="JB100" t="n">
         <v>0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.005536997690796852</v>
+        <v>-0.005537047050893307</v>
       </c>
       <c r="JB101" t="n">
         <v>0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.005343656055629253</v>
+        <v>-0.005343695171177387</v>
       </c>
       <c r="JB102" t="n">
         <v>0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.005072209052741528</v>
+        <v>-0.005072243511676788</v>
       </c>
       <c r="JB103" t="n">
         <v>0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.004878522828221321</v>
+        <v>-0.004878602921962738</v>
       </c>
       <c r="JB104" t="n">
         <v>0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.004797053523361683</v>
+        <v>-0.004797122441232204</v>
       </c>
       <c r="JB105" t="n">
         <v>0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.004662945866584778</v>
+        <v>-0.004662986844778061</v>
       </c>
       <c r="JB106" t="n">
         <v>0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.004520243965089321</v>
+        <v>-0.00452027190476656</v>
       </c>
       <c r="JB107" t="n">
         <v>0.3999999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.004333194345235825</v>
+        <v>-0.00433320552110672</v>
       </c>
       <c r="JB108" t="n">
         <v>0.3999999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.004098003730177879</v>
+        <v>-0.004098009318113327</v>
       </c>
       <c r="JB109" t="n">
         <v>0.3999999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.003852915018796921</v>
+        <v>-0.003852947615087032</v>
       </c>
       <c r="JB110" t="n">
         <v>0.3999999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.003748527728021145</v>
+        <v>-0.003748533315956593</v>
       </c>
       <c r="JB111" t="n">
         <v>0.3999999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.003690445795655251</v>
+        <v>-0.003690457902848721</v>
       </c>
       <c r="JB112" t="n">
         <v>0.3999999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.003592804074287415</v>
+        <v>-0.003592828288674355</v>
       </c>
       <c r="JB113" t="n">
         <v>0.3999999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.00345512293279171</v>
+        <v>-0.003455153666436672</v>
       </c>
       <c r="JB114" t="n">
         <v>0.3999999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.003404975868761539</v>
+        <v>-0.00340499822050333</v>
       </c>
       <c r="JB115" t="n">
         <v>0.3999999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.00336892157793045</v>
+        <v>-0.003368925303220749</v>
       </c>
       <c r="JB116" t="n">
         <v>0.3999999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.003369292244315147</v>
+        <v>-0.003369287587702274</v>
       </c>
       <c r="JB117" t="n">
         <v>0.3999999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.003233139403164387</v>
+        <v>-0.003233159892261028</v>
       </c>
       <c r="JB118" t="n">
         <v>0.2599999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.003182061016559601</v>
+        <v>-0.00318207498639822</v>
       </c>
       <c r="JB119" t="n">
         <v>0.1199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.003499255515635014</v>
+        <v>-0.003499263897538185</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.02000000000000007</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.003777755424380302</v>
+        <v>-0.003777753561735153</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.16</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.003874681890010834</v>
+        <v>-0.003874707967042923</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.003947744145989418</v>
+        <v>-0.003947778604924679</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.00377553328871727</v>
+        <v>-0.003775548189878464</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.01999999999999985</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.003649835474789143</v>
+        <v>-0.00364984106272459</v>
       </c>
       <c r="JB126" t="n">
         <v>0.1200000000000001</v>
